--- a/reports/devops-juniors-israel-2026-W44.xlsx
+++ b/reports/devops-juniors-israel-2026-W44.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-26T12:49:07</t>
+    <t xml:space="preserve">2026-10-27T12:02:48</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,12 +94,12 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -181,7 +181,172 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
   </si>
   <si>
     <t xml:space="preserve">SAP</t>
@@ -190,157 +355,418 @@
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-technician-at-confidential-careers-4481091143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4481089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Physicist / System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEQA Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (375770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
     <t xml:space="preserve">System Integration Student, SPIV team</t>
@@ -352,429 +778,12 @@
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (37866)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-technician-at-confidential-careers-4481091143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4481089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Physicist / System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEQA Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (375770)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-peax-4481439767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -784,30 +793,30 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -826,6 +835,12 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
@@ -838,12 +853,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -877,12 +886,12 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
@@ -896,9 +905,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -1026,7 +1032,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -1034,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1050,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
@@ -1132,7 +1138,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1156,7 +1162,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1182,7 +1188,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -1190,7 +1196,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1264,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1322,7 +1328,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1369,7 +1375,7 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1377,31 +1383,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1409,31 +1415,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1441,31 +1447,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1497,7 +1503,7 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1505,31 +1511,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1537,19 +1543,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>98</v>
@@ -1575,25 +1581,25 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1601,31 +1607,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
         <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1633,31 +1639,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1665,31 +1671,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1697,31 +1703,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1729,31 +1735,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1761,31 +1767,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -1793,31 +1799,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -1825,13 +1831,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1840,16 +1846,16 @@
         <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -1857,31 +1863,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22">
@@ -1889,31 +1895,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
@@ -1921,13 +1927,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1936,16 +1942,16 @@
         <v>44</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
@@ -1953,31 +1959,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F24" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25">
@@ -1985,31 +1991,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
@@ -2017,13 +2023,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2032,16 +2038,16 @@
         <v>36</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2100,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2109,22 +2115,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2">
@@ -2138,7 +2144,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2147,7 +2153,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2159,7 +2165,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2182,7 +2188,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2194,7 +2200,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2208,7 +2214,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2217,7 +2223,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2229,7 +2235,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -2252,7 +2258,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2261,115 +2267,115 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2392,7 +2398,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2401,68 +2407,68 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2474,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="K11" s="3">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -2485,287 +2491,287 @@
         <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="K14" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K15" s="3">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K18" s="3">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2774,103 +2780,103 @@
         <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K20" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K22" s="3">
-        <v>61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2879,19 +2885,19 @@
         <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="K23" s="3">
         <v>1</v>
@@ -2899,83 +2905,83 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E24" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K25" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -2984,103 +2990,103 @@
         <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="K26" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="K28" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3089,138 +3095,138 @@
         <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E30" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K30" s="3">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
         <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K32" s="3">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3229,33 +3235,33 @@
         <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="K33" s="3">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3264,339 +3270,302 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>145</v>
+        <v>217</v>
       </c>
       <c r="K34" s="3">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K35" s="3">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>224</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="K37" s="3">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="K38" s="3">
-        <v>73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="K39" s="3">
-        <v>73</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="K40" s="3">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>163</v>
+        <v>248</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>250</v>
       </c>
       <c r="K41" s="3">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>245</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="K42" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K43" s="3">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3639,7 +3608,6 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3647,11 +3615,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3670,10 +3638,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3681,127 +3649,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>48</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3816,178 +3688,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4007,10 +3879,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
@@ -4018,10 +3890,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -4032,7 +3904,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4">
@@ -4043,7 +3915,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5">
@@ -4051,10 +3923,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6">
@@ -4065,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4086,13 +3958,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2">
@@ -4100,10 +3972,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4112,22 +3984,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W44.xlsx
+++ b/reports/devops-juniors-israel-2026-W44.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27T12:02:48</t>
+    <t xml:space="preserve">2026-10-28T12:41:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,445 +217,469 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annapurna Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-confidential-careers-4482513067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4481089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Physicist / System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEQA Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4483213993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (37866)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483535843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
+    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (375770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC / NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-noc-analyst-at-radware-4482280964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-at-shavit-software-4484431493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Operations Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4483540095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-technician-at-confidential-careers-4481091143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4481089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Physicist / System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEQA Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (375770)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
+    <t xml:space="preserve">AWS, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-compie-technologies-4483368453</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
@@ -736,6 +760,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
   </si>
   <si>
+    <t xml:space="preserve">Application Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGone Consultants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-support-engineer-at-bgone-consultants-4481893131</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -766,145 +799,130 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -1032,7 +1050,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1040,7 +1058,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1056,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -1138,7 +1156,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1146,7 +1164,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1188,7 +1206,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1392,10 +1410,10 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
@@ -1424,10 +1442,10 @@
         <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>76</v>
@@ -1439,7 +1457,7 @@
         <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1447,13 +1465,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1462,16 +1480,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1488,10 +1506,10 @@
         <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>87</v>
@@ -1517,25 +1535,25 @@
         <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>80</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3">
-        <v>83</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1543,25 +1561,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>99</v>
@@ -1578,28 +1596,28 @@
         <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
         <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -1607,31 +1625,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1639,13 +1657,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1654,16 +1672,16 @@
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1671,13 +1689,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
@@ -1686,16 +1704,16 @@
         <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1703,10 +1721,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>57</v>
@@ -1718,16 +1736,16 @@
         <v>61</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1753,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>28</v>
@@ -1750,16 +1768,16 @@
         <v>57</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1767,13 +1785,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1782,16 +1800,16 @@
         <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -1799,13 +1817,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -1814,16 +1832,16 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -1831,31 +1849,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>48</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -1863,31 +1881,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>44</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="3">
-        <v>46</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="22">
@@ -1895,13 +1913,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1919,7 +1937,7 @@
         <v>158</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
@@ -1927,31 +1945,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="3">
+        <v>41</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>44</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="24">
@@ -1965,25 +1983,25 @@
         <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>36</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="3">
-        <v>41</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="25">
@@ -1991,13 +2009,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2006,16 +2024,16 @@
         <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="26">
@@ -2023,31 +2041,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2100,7 +2118,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2115,22 +2133,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
@@ -2153,7 +2171,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2165,7 +2183,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2188,7 +2206,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2200,7 +2218,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -2223,7 +2241,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2235,7 +2253,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -2258,7 +2276,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2270,7 +2288,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -2284,16 +2302,16 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2305,7 +2323,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2319,16 +2337,16 @@
         <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2337,21 +2355,21 @@
         <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K7" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2360,22 +2378,22 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2389,16 +2407,16 @@
         <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2410,7 +2428,7 @@
         <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2421,57 +2439,57 @@
         <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>80</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>83</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="K10" s="3">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>99</v>
@@ -2480,7 +2498,7 @@
         <v>100</v>
       </c>
       <c r="K11" s="3">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2488,80 +2506,80 @@
         <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="K12" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="K13" s="3">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
@@ -2570,33 +2588,33 @@
         <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K14" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
@@ -2605,30 +2623,30 @@
         <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="K15" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>57</v>
@@ -2640,33 +2658,33 @@
         <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="K16" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>28</v>
@@ -2675,33 +2693,33 @@
         <v>57</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2710,33 +2728,33 @@
         <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
@@ -2745,103 +2763,103 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K19" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3">
+        <v>46</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>48</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K20" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>44</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3">
-        <v>46</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="K21" s="3">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2853,7 +2871,7 @@
         <v>157</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
@@ -2862,7 +2880,7 @@
         <v>158</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="K22" s="3">
         <v>2</v>
@@ -2870,37 +2888,37 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="3">
+        <v>41</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2911,42 +2929,42 @@
         <v>166</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>36</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="3">
-        <v>41</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K24" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2955,103 +2973,103 @@
         <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="K25" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="K26" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>34</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K27" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3060,33 +3078,33 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3095,33 +3113,33 @@
         <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="K29" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>29</v>
@@ -3130,33 +3148,33 @@
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K30" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
@@ -3165,33 +3183,33 @@
         <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K31" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3200,33 +3218,33 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K32" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3235,33 +3253,33 @@
         <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K33" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3270,22 +3288,22 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="K34" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3296,136 +3314,136 @@
         <v>219</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>24</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="K35" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>24</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="J36" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>20</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K36" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>20</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K37" s="3">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="K38" s="3">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
@@ -3436,136 +3454,208 @@
         <v>238</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="K39" s="3">
-        <v>14</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="K40" s="3">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="K41" s="3">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E43" s="3">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K43" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K42" s="3">
-        <v>68</v>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K44"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3608,6 +3698,8 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3615,11 +3707,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3638,10 +3730,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3649,31 +3741,149 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
         <v>28</v>
       </c>
-      <c r="D2" s="3">
-        <v>57</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>132</v>
+      <c r="E3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3688,178 +3898,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3879,10 +4089,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2">
@@ -3890,10 +4100,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
@@ -3901,10 +4111,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -3915,7 +4125,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5">
@@ -3926,7 +4136,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -3937,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3958,13 +4168,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2">
@@ -3975,7 +4185,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3984,22 +4194,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W44.xlsx
+++ b/reports/devops-juniors-israel-2026-W44.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-28T12:41:55</t>
+    <t xml:space="preserve">2026-10-29T12:50:47</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -181,6 +184,24 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">BLE System Test DevOps Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas Instruments Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ble-system-test-devops-intern-at-texas-instruments-europe-4484112036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -301,24 +322,6 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
@@ -349,9 +352,6 @@
     <t xml:space="preserve">SAP</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -526,18 +526,6 @@
     <t xml:space="preserve">2026-10-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Service Desk Team Leader</t>
   </si>
   <si>
@@ -553,6 +541,15 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator (375770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -571,15 +568,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (375770)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-375770-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4483527986</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -670,18 +658,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-at-shavit-software-4484431493</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-compie-technologies-4483368453</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -814,15 +790,15 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
@@ -838,16 +814,40 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
@@ -856,40 +856,16 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -911,6 +887,9 @@
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1050,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -1058,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1066,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1074,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -1156,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1164,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1192,29 +1171,37 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>36</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1238,34 +1225,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1273,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>26</v>
@@ -1288,16 +1275,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1305,13 +1292,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>25</v>
@@ -1320,16 +1307,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1337,31 +1324,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1369,13 +1356,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1384,16 +1371,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1401,31 +1388,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1433,31 +1420,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -1465,13 +1452,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1480,16 +1467,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1497,31 +1484,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3">
-        <v>83</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -1529,31 +1516,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -1561,31 +1548,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -1593,13 +1580,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1608,16 +1595,16 @@
         <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -1625,13 +1612,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1640,16 +1627,16 @@
         <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -1657,13 +1644,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1675,7 +1662,7 @@
         <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>113</v>
@@ -1707,7 +1694,7 @@
         <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>119</v>
@@ -1727,7 +1714,7 @@
         <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
@@ -1739,7 +1726,7 @@
         <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -1771,7 +1758,7 @@
         <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>130</v>
@@ -1803,7 +1790,7 @@
         <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>136</v>
@@ -1835,7 +1822,7 @@
         <v>141</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>142</v>
@@ -1867,7 +1854,7 @@
         <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>147</v>
@@ -1899,7 +1886,7 @@
         <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>152</v>
@@ -1931,7 +1918,7 @@
         <v>157</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>158</v>
@@ -1963,7 +1950,7 @@
         <v>162</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>163</v>
@@ -1983,7 +1970,7 @@
         <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -1995,7 +1982,7 @@
         <v>167</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>168</v>
@@ -2012,28 +1999,28 @@
         <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26">
@@ -2041,31 +2028,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>28</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>34</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2118,48 +2105,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>26</v>
@@ -2168,33 +2155,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
@@ -2203,68 +2190,68 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2273,103 +2260,103 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>13</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="K7" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2378,138 +2365,138 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K8" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>83</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>27</v>
@@ -2518,33 +2505,33 @@
         <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K12" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>27</v>
@@ -2553,33 +2540,33 @@
         <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K13" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
@@ -2591,10 +2578,10 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>113</v>
@@ -2603,7 +2590,7 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -2626,10 +2613,10 @@
         <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>119</v>
@@ -2638,7 +2625,7 @@
         <v>120</v>
       </c>
       <c r="K15" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -2649,7 +2636,7 @@
         <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2661,10 +2648,10 @@
         <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -2673,7 +2660,7 @@
         <v>125</v>
       </c>
       <c r="K16" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -2696,10 +2683,10 @@
         <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>130</v>
@@ -2708,7 +2695,7 @@
         <v>131</v>
       </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2731,10 +2718,10 @@
         <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>136</v>
@@ -2743,7 +2730,7 @@
         <v>137</v>
       </c>
       <c r="K18" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2766,10 +2753,10 @@
         <v>141</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>142</v>
@@ -2778,7 +2765,7 @@
         <v>143</v>
       </c>
       <c r="K19" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2801,10 +2788,10 @@
         <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>147</v>
@@ -2813,7 +2800,7 @@
         <v>148</v>
       </c>
       <c r="K20" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -2836,10 +2823,10 @@
         <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>152</v>
@@ -2848,7 +2835,7 @@
         <v>153</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2871,10 +2858,10 @@
         <v>157</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>158</v>
@@ -2883,7 +2870,7 @@
         <v>137</v>
       </c>
       <c r="K22" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2906,10 +2893,10 @@
         <v>162</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>163</v>
@@ -2918,7 +2905,7 @@
         <v>164</v>
       </c>
       <c r="K23" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2929,7 +2916,7 @@
         <v>166</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -2941,10 +2928,10 @@
         <v>167</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>168</v>
@@ -2953,7 +2940,7 @@
         <v>169</v>
       </c>
       <c r="K24" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -2961,80 +2948,80 @@
         <v>170</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="K25" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>28</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>34</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="K26" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3043,33 +3030,33 @@
         <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>137</v>
+        <v>67</v>
       </c>
       <c r="K27" s="3">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>189</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3078,57 +3065,57 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="K28" s="3">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E29" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>195</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -3139,77 +3126,77 @@
         <v>197</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="K30" s="3">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K31" s="3">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3221,30 +3208,30 @@
         <v>209</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>210</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>211</v>
+        <v>143</v>
       </c>
       <c r="K32" s="3">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3253,33 +3240,33 @@
         <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="K33" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3288,22 +3275,22 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
@@ -3314,136 +3301,136 @@
         <v>219</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K36" s="3">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="K37" s="3">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>232</v>
+        <v>165</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>20</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K38" s="3">
-        <v>75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -3454,208 +3441,138 @@
         <v>238</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="K39" s="3">
-        <v>75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>244</v>
+        <v>153</v>
       </c>
       <c r="K40" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="K41" s="3">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>6</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>153</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K43" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K44"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3698,8 +3615,6 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3707,9 +3622,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3718,172 +3633,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>24</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3898,178 +3695,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -4086,13 +3883,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2">
@@ -4100,10 +3897,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -4111,10 +3908,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4">
@@ -4125,7 +3922,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5">
@@ -4136,7 +3933,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6">
@@ -4147,7 +3944,18 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4165,51 +3973,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W44.xlsx
+++ b/reports/devops-juniors-israel-2026-W44.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-29T12:50:47</t>
+    <t xml:space="preserve">2026-10-30T12:42:50</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,10 +94,13 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+    <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
@@ -106,9 +109,6 @@
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -166,6 +166,24 @@
     <t xml:space="preserve">2026-10-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Databases, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-simplex-3d-4449504561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
@@ -277,60 +295,63 @@
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471963869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Integration Student, SPIV team</t>
   </si>
   <si>
@@ -445,24 +466,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Technician</t>
   </si>
   <si>
@@ -583,9 +586,6 @@
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -628,9 +628,6 @@
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -688,63 +685,48 @@
     <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">AU10TIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-at-au10tix-4483009897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4483012789</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-16</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BGone Consultants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-support-engineer-at-bgone-consultants-4481893131</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -814,60 +796,60 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -877,19 +859,19 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1029,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1037,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1053,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -1135,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1143,7 +1125,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1151,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1159,7 +1141,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1175,7 +1157,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1193,7 +1175,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1269,7 +1251,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1301,7 +1283,7 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1333,7 +1315,7 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1365,7 +1347,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1429,10 +1411,10 @@
         <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>77</v>
@@ -1461,10 +1443,10 @@
         <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>83</v>
@@ -1476,7 +1458,7 @@
         <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1484,13 +1466,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -1499,16 +1481,16 @@
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -1525,10 +1507,10 @@
         <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>94</v>
@@ -1554,25 +1536,25 @@
         <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -1580,31 +1562,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -1612,31 +1594,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1644,31 +1626,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
         <v>70</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1676,31 +1658,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1708,31 +1690,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1740,31 +1722,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1772,31 +1754,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -1804,31 +1786,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -1836,31 +1818,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -1868,13 +1850,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1883,16 +1865,16 @@
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22">
@@ -1900,13 +1882,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1915,16 +1897,16 @@
         <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
@@ -1932,31 +1914,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3">
         <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
@@ -1964,13 +1946,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -1979,16 +1961,16 @@
         <v>36</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25">
@@ -1996,31 +1978,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
         <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -2028,13 +2010,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2043,16 +2025,16 @@
         <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2087,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2120,22 +2102,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
@@ -2149,7 +2131,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2158,7 +2140,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2170,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2184,7 +2166,7 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2193,7 +2175,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2205,7 +2187,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2219,7 +2201,7 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2228,7 +2210,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2240,7 +2222,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -2254,7 +2236,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2263,7 +2245,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2275,7 +2257,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2298,7 +2280,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2310,7 +2292,7 @@
         <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -2324,16 +2306,16 @@
         <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2345,7 +2327,7 @@
         <v>79</v>
       </c>
       <c r="K7" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2359,16 +2341,16 @@
         <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2377,21 +2359,21 @@
         <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="K8" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
@@ -2400,22 +2382,22 @@
         <v>84</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="K9" s="3">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2429,16 +2411,16 @@
         <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2450,7 +2432,7 @@
         <v>96</v>
       </c>
       <c r="K10" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2461,273 +2443,273 @@
         <v>98</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K11" s="3">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="K12" s="3">
-        <v>29</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
         <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K15" s="3">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E18" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K18" s="3">
         <v>3</v>
@@ -2735,83 +2717,83 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="K20" s="3">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2820,33 +2802,33 @@
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2855,68 +2837,68 @@
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="3">
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K23" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -2925,68 +2907,68 @@
         <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K24" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
         <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K25" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -2995,33 +2977,33 @@
         <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3030,33 +3012,33 @@
         <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K27" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3068,7 +3050,7 @@
         <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
@@ -3077,10 +3059,10 @@
         <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -3091,10 +3073,10 @@
         <v>193</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" s="3">
         <v>27</v>
@@ -3103,7 +3085,7 @@
         <v>194</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3112,10 +3094,10 @@
         <v>195</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K29" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -3129,7 +3111,7 @@
         <v>198</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
         <v>27</v>
@@ -3138,7 +3120,7 @@
         <v>199</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
@@ -3150,7 +3132,7 @@
         <v>201</v>
       </c>
       <c r="K30" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
@@ -3161,7 +3143,7 @@
         <v>203</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>52</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3170,33 +3152,33 @@
         <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="K31" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3205,33 +3187,33 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="K32" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3240,33 +3222,33 @@
         <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3275,138 +3257,138 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="K34" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="K35" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>20</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>201</v>
       </c>
       <c r="K36" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>8</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="K37" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>233</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3415,33 +3397,33 @@
         <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>236</v>
+        <v>55</v>
       </c>
       <c r="K38" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3450,57 +3432,57 @@
         <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="K39" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
@@ -3514,65 +3496,30 @@
         <v>245</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>246</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="K41" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K41"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3614,7 +3561,6 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3622,9 +3568,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3645,10 +3591,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -3656,31 +3602,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3695,178 +3689,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B2" s="3">
         <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B3" s="3">
         <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3886,10 +3880,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
@@ -3897,10 +3891,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -3908,10 +3902,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -3919,10 +3913,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -3930,10 +3924,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
@@ -3944,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
@@ -3952,10 +3946,10 @@
         <v>30</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3976,13 +3970,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
@@ -3993,7 +3987,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4005,19 +3999,19 @@
         <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D4" s="3"/>
     </row>
